--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1659,6 +1659,118 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73676931</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136807915</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ingvallhögen, Ingvallhögen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>377803</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6780616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136807915</t>
         </is>
       </c>
     </row>
@@ -1673,6 +1785,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 2004-2020 artfynd.xlsx
+++ b/artfynd/S 2004-2020 artfynd.xlsx
@@ -1667,7 +1667,7 @@
         <v>136807915</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
